--- a/Exp3_PTO_GRPO/eda/results/L0/tables/6_stats/6_stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L0/tables/6_stats/6_stats.xlsx
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.71</v>
+        <v>2.858</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
       <c r="G5" t="n">
-        <v>0.592</v>
+        <v>0.658</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -687,16 +687,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.413</v>
+        <v>0.439</v>
       </c>
       <c r="K5" t="n">
         <v>0.8159999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0396</v>
+        <v>0.0401</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.691</v>
+        <v>2.837</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.845</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.954</v>
+        <v>0.899</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.66</v>
+        <v>0.637</v>
       </c>
       <c r="K14" t="n">
-        <v>1.023</v>
+        <v>0.997</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0885</v>
+        <v>0.0818</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1603,16 +1603,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.71</v>
+        <v>2.858</v>
       </c>
       <c r="E23" t="n">
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.616</v>
+        <v>0.583</v>
       </c>
       <c r="G23" t="n">
-        <v>0.767</v>
+        <v>0.716</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1623,16 +1623,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.463</v>
+        <v>0.425</v>
       </c>
       <c r="K23" t="n">
-        <v>0.778</v>
+        <v>0.753</v>
       </c>
       <c r="L23" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0396</v>
+        <v>0.0401</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2071,16 +2071,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.691</v>
+        <v>2.837</v>
       </c>
       <c r="E32" t="n">
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>0.845</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.954</v>
+        <v>0.899</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2091,16 +2091,16 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.66</v>
+        <v>0.637</v>
       </c>
       <c r="K32" t="n">
-        <v>1.023</v>
+        <v>0.997</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0885</v>
+        <v>0.0818</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>129.4716</v>
+        <v>129.3604</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1349</v>
+        <v>0.1348</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>191.6901</v>
+        <v>183.4767</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1997</v>
+        <v>0.1911</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
@@ -3726,13 +3726,13 @@
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1372</v>
+        <v>-0.0799</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1481</v>
+        <v>-0.0935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.657</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3951,10 +3951,10 @@
         <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0017</v>
+        <v>0.0156</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0018</v>
+        <v>0.0154</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -4157,7 +4157,7 @@
         <v>-0.22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1791</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="23">
@@ -4176,13 +4176,13 @@
         <v>96</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2118</v>
+        <v>-0.184</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2455</v>
+        <v>-0.2371</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1791</v>
+        <v>0.1277</v>
       </c>
     </row>
     <row r="24">
@@ -4307,7 +4307,7 @@
         <v>-0.242</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1791</v>
+        <v>0.1538</v>
       </c>
     </row>
     <row r="29">
@@ -4401,10 +4401,10 @@
         <v>96</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0556</v>
+        <v>-0.0313</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0413</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -4626,10 +4626,10 @@
         <v>96</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0486</v>
+        <v>0.0503</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0593</v>
+        <v>0.0623</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -4782,7 +4782,7 @@
         <v>0.3238</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0786</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="48">
@@ -4832,7 +4832,7 @@
         <v>0.1972</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2856</v>
+        <v>0.2609</v>
       </c>
     </row>
     <row r="50">
@@ -4851,13 +4851,13 @@
         <v>96</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1406</v>
+        <v>0.224</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1863</v>
+        <v>0.3042</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2856</v>
+        <v>0.0346</v>
       </c>
     </row>
     <row r="51">
@@ -4932,7 +4932,7 @@
         <v>0.2465</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0987</v>
+        <v>0.08459999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4982,7 +4982,7 @@
         <v>0.2736</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1419</v>
+        <v>0.1183</v>
       </c>
     </row>
     <row r="56">
@@ -5076,10 +5076,10 @@
         <v>96</v>
       </c>
       <c r="E59" t="n">
-        <v>0.033</v>
+        <v>0.0278</v>
       </c>
       <c r="F59" t="n">
-        <v>0.038</v>
+        <v>0.0334</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -5301,13 +5301,13 @@
         <v>96</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1024</v>
+        <v>0.1128</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1293</v>
+        <v>0.1558</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4445</v>
+        <v>0.2233</v>
       </c>
     </row>
     <row r="69">
@@ -5432,7 +5432,7 @@
         <v>0.2577</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2999</v>
+        <v>0.2399</v>
       </c>
     </row>
     <row r="74">
@@ -5526,10 +5526,10 @@
         <v>96</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6632</v>
+        <v>0.5833</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8349</v>
+        <v>0.7663</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -5751,10 +5751,10 @@
         <v>96</v>
       </c>
       <c r="E86" t="n">
-        <v>0.217</v>
+        <v>0.1736</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2817</v>
+        <v>0.2668</v>
       </c>
       <c r="G86" t="n">
         <v>0.0146</v>
@@ -6015,13 +6015,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1044</v>
+        <v>0.1032</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0396</v>
+        <v>0.0401</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
@@ -6231,13 +6231,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.1995</v>
+        <v>0.1879</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0885</v>
+        <v>0.0818</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
     </row>
   </sheetData>
